--- a/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>76.574.879-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14212,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14277,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14342,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14407,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14472,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14537,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14602,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14667,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14732,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14797,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14862,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14927,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14992,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +15057,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +15122,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +15187,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15252,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15317,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15382,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15447,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15512,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15577,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15642,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15707,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15772,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15837,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15902,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15967,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +16032,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +16097,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +16162,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16227,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16292,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16357,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16422,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16487,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16552,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16617,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16682,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16747,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16812,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16877,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16942,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +17007,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +17072,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +17137,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +17202,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17267,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17332,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17397,11 @@
           <t>89.862.200-2</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>889473-1594-CM25</t>
+          <t>889473-1593-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>67.61</v>
+        <v>183.64</v>
       </c>
     </row>
     <row r="91">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>889473-1593-CM25</t>
+          <t>889473-1594-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>183.64</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="98">
@@ -7014,7 +7014,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3016-369-CM25</t>
+          <t>1739-16-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.090.500-0</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOLOL</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>146.87</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1739-16-CM25</t>
+          <t>3016-369-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>69.090.500-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>146.87</v>
+        <v>90.70999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7924,7 +7924,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>889473-2008-CM25</t>
+          <t>889473-2001-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>222.19</v>
+        <v>183.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>889473-2001-CM25</t>
+          <t>889473-2008-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>183.6</v>
+        <v>222.19</v>
       </c>
     </row>
     <row r="118">
@@ -9029,7 +9029,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>889473-2288-CM25</t>
+          <t>1562-596-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>308.42</v>
+        <v>154.79</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>591-7579-CM25</t>
+          <t>889473-2288-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>201.25</v>
+        <v>308.42</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1562-596-CM25</t>
+          <t>591-7579-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>154.79</v>
+        <v>201.25</v>
       </c>
     </row>
     <row r="136">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1402-783-CM25</t>
+          <t>1402-782-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>183.76</v>
+        <v>482.32</v>
       </c>
     </row>
     <row r="142">
@@ -9679,7 +9679,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1402-782-CM25</t>
+          <t>1402-783-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>482.32</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="144">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>889473-513-CM26</t>
+          <t>889473-516-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>396.52</v>
+        <v>221.71</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>889473-516-CM26</t>
+          <t>889473-513-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>221.71</v>
+        <v>396.52</v>
       </c>
     </row>
     <row r="182">
@@ -12734,7 +12734,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>889473-680-CM26</t>
+          <t>4562-243-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>176.25</v>
+        <v>319.29</v>
       </c>
     </row>
     <row r="191">
@@ -12864,7 +12864,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4562-243-CM26</t>
+          <t>889473-680-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12884,17 +12884,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>319.29</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="193">
@@ -13384,7 +13384,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1743-278-CM26</t>
+          <t>2817-307-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13404,17 +13404,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>164.21</v>
+        <v>158.09</v>
       </c>
     </row>
     <row r="201">
@@ -13514,7 +13514,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2817-307-CM26</t>
+          <t>1743-278-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13534,17 +13534,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13573,7 +13573,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>158.09</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="203">
@@ -14034,7 +14034,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4562-290-CM26</t>
+          <t>3994-151-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14054,17 +14054,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14093,18 +14093,18 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>380.76</v>
+        <v>209.79</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4562-291-SE26</t>
+          <t>3634-248-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14139,12 +14139,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14158,18 +14158,18 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>116.58</v>
+        <v>386.78</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2675-234-CM26</t>
+          <t>4562-291-SE26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14184,17 +14184,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>636.96</v>
+        <v>116.58</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3634-248-CM26</t>
+          <t>4562-290-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>386.78</v>
+        <v>380.76</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3994-151-CM26</t>
+          <t>2675-234-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>209.79</v>
+        <v>636.96</v>
       </c>
     </row>
     <row r="215">
@@ -15204,7 +15204,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>591-212-CM26</t>
+          <t>591-208-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>341.05</v>
+        <v>331.11</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>591-211-CM26</t>
+          <t>591-210-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>341.05</v>
+        <v>331.11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>591-210-CM26</t>
+          <t>591-211-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>331.11</v>
+        <v>341.05</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>591-208-CM26</t>
+          <t>591-212-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>331.11</v>
+        <v>341.05</v>
       </c>
     </row>
     <row r="232">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>889473-1511-CM26</t>
+          <t>889473-1515-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>261.2</v>
+        <v>286.38</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1402-503-CM26</t>
+          <t>1402-504-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>229.32</v>
+        <v>286.54</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1402-504-CM26</t>
+          <t>889473-1511-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>286.54</v>
+        <v>261.2</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>889473-1515-CM26</t>
+          <t>1402-503-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>286.38</v>
+        <v>229.32</v>
       </c>
     </row>
     <row r="245">
@@ -16829,12 +16829,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>889473-1707-CM26</t>
+          <t>1402-548-SE26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -16844,22 +16844,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,18 +16888,18 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>145.13</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>889473-1713-CM26</t>
+          <t>1402-547-SE26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -16909,22 +16909,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16934,12 +16934,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>321.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>889473-1715-CM26</t>
+          <t>889473-1707-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16999,12 +16999,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>168.6</v>
+        <v>145.13</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>889473-1746-CM26</t>
+          <t>889473-1713-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>214.1</v>
+        <v>321.7</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>889473-1744-CM26</t>
+          <t>889473-1715-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>203.87</v>
+        <v>168.6</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>889473-1766-CM26</t>
+          <t>889473-1744-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>139.71</v>
+        <v>203.87</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1208100-30-CM26</t>
+          <t>889473-1746-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>642.91</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>889473-1763-CM26</t>
+          <t>889473-1766-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17343,71 +17343,201 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>184.48</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
+          <t>1208100-30-CM26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>642.91</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>889473-1763-CM26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>184.48</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>1208100-31-CM26</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
         <is>
           <t>62.000.890-7</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G263" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>89.862.200-2</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M261" s="2" t="n">
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
         <v>152.79</v>
       </c>
     </row>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>889473-1595-CM25</t>
+          <t>889473-1594-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>92.86</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>889473-1596-CM25</t>
+          <t>889473-1595-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>45.48</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>889473-1597-CM25</t>
+          <t>889473-1596-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>97.86</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>889473-1598-CM25</t>
+          <t>889473-1597-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>45.48</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="95">
@@ -6689,7 +6689,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>889473-1594-CM25</t>
+          <t>889473-1598-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>67.61</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="98">
@@ -7794,7 +7794,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>889473-1978-CM25</t>
+          <t>889473-1984-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>407.55</v>
+        <v>242.64</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>889473-1984-CM25</t>
+          <t>889473-1978-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>242.64</v>
+        <v>407.55</v>
       </c>
     </row>
     <row r="116">
@@ -8704,7 +8704,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>889473-2225-CM25</t>
+          <t>889473-2230-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>183.4</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>889473-2230-CM25</t>
+          <t>889473-2234-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>98.98999999999999</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>889473-2234-CM25</t>
+          <t>889473-2235-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>105.36</v>
+        <v>1097.46</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>889473-2235-CM25</t>
+          <t>889473-2225-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1097.46</v>
+        <v>183.4</v>
       </c>
     </row>
     <row r="132">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1402-782-CM25</t>
+          <t>1402-783-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>482.32</v>
+        <v>183.76</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>997-177-CM25</t>
+          <t>1402-782-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>856.22</v>
+        <v>482.32</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1402-783-CM25</t>
+          <t>997-177-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>183.76</v>
+        <v>856.22</v>
       </c>
     </row>
     <row r="144">
@@ -11109,7 +11109,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2817-24-CM26</t>
+          <t>2817-26-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>237.16</v>
+        <v>297.03</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2817-26-CM26</t>
+          <t>2817-24-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>297.03</v>
+        <v>237.16</v>
       </c>
     </row>
     <row r="167">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>889473-394-CM26</t>
+          <t>889473-395-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>83.2</v>
+        <v>218.45</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>889473-395-CM26</t>
+          <t>889473-394-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>218.45</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="176">
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>932-60-CM26</t>
+          <t>932-62-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>534.14</v>
+        <v>242.13</v>
       </c>
     </row>
     <row r="185">
@@ -12474,7 +12474,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>932-62-CM26</t>
+          <t>932-60-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>242.13</v>
+        <v>534.14</v>
       </c>
     </row>
     <row r="187">
@@ -12929,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3948-131-CM26</t>
+          <t>889473-707-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>253.71</v>
+        <v>1698.02</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>889473-707-CM26</t>
+          <t>3948-131-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1698.02</v>
+        <v>253.71</v>
       </c>
     </row>
     <row r="195">
@@ -13449,7 +13449,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4562-270-CM26</t>
+          <t>1743-278-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>88.53</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1743-278-CM26</t>
+          <t>4562-270-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13534,17 +13534,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13573,7 +13573,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>164.21</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="203">
@@ -13644,7 +13644,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>4164-261-CM26</t>
+          <t>3014-162-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.080.600-2</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE DONIHUE</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>366.5</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -13774,7 +13774,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3014-162-CM26</t>
+          <t>4164-261-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.080.600-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE DONIHUE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>84.68000000000001</v>
+        <v>366.5</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2401-544-CM26</t>
+          <t>2401-546-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>826.79</v>
+        <v>165.36</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2401-546-CM26</t>
+          <t>2401-544-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13963,7 +13963,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>165.36</v>
+        <v>826.79</v>
       </c>
     </row>
     <row r="209">
@@ -14034,7 +14034,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3994-151-CM26</t>
+          <t>4562-290-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14054,17 +14054,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>209.79</v>
+        <v>380.76</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3634-248-CM26</t>
+          <t>2675-234-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14158,18 +14158,18 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>386.78</v>
+        <v>636.96</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4562-291-SE26</t>
+          <t>3634-248-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>116.58</v>
+        <v>386.78</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4562-290-CM26</t>
+          <t>3994-151-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14249,17 +14249,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -14288,18 +14288,18 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>380.76</v>
+        <v>209.79</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2675-234-CM26</t>
+          <t>4562-291-SE26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -14314,17 +14314,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>636.96</v>
+        <v>116.58</v>
       </c>
     </row>
     <row r="215">
@@ -14424,7 +14424,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2401-569-CM26</t>
+          <t>3889-279-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14449,12 +14449,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.090.200-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PLACILLA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>249.88</v>
+        <v>1200.66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3889-279-CM26</t>
+          <t>2401-569-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14514,12 +14514,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.090.200-1</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PLACILLA</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1200.66</v>
+        <v>249.88</v>
       </c>
     </row>
     <row r="218">
@@ -14619,7 +14619,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>889473-962-CM26</t>
+          <t>889473-957-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14659,12 +14659,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>172.34</v>
+        <v>193.67</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>889473-957-CM26</t>
+          <t>889473-962-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>193.67</v>
+        <v>172.34</v>
       </c>
     </row>
     <row r="221">
@@ -15009,7 +15009,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>889473-1084-CM26</t>
+          <t>889473-1086-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>456.6</v>
+        <v>122.15</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>889473-1086-CM26</t>
+          <t>889473-1084-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>122.15</v>
+        <v>456.6</v>
       </c>
     </row>
     <row r="227">
@@ -15204,7 +15204,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>591-208-CM26</t>
+          <t>591-211-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>331.11</v>
+        <v>341.05</v>
       </c>
     </row>
     <row r="229">
@@ -15334,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>591-211-CM26</t>
+          <t>591-208-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15393,7 +15393,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>341.05</v>
+        <v>331.11</v>
       </c>
     </row>
     <row r="231">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>932-143-CM26</t>
+          <t>932-144-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>604.55</v>
+        <v>851.55</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>932-144-CM26</t>
+          <t>932-143-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>851.55</v>
+        <v>604.55</v>
       </c>
     </row>
     <row r="237">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>889473-1515-CM26</t>
+          <t>1402-503-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>286.38</v>
+        <v>229.32</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1402-504-CM26</t>
+          <t>889473-1511-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,17 +16134,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>286.54</v>
+        <v>261.2</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>889473-1511-CM26</t>
+          <t>889473-1515-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>261.2</v>
+        <v>286.38</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1402-503-CM26</t>
+          <t>1402-504-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>229.32</v>
+        <v>286.54</v>
       </c>
     </row>
     <row r="245">
@@ -16634,7 +16634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>889473-1667-CM26</t>
+          <t>932-165-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,12 +16659,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>122.51</v>
+        <v>2095.47</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>932-165-CM26</t>
+          <t>889473-1667-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16724,12 +16724,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2095.47</v>
+        <v>122.51</v>
       </c>
     </row>
     <row r="252">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1402-548-SE26</t>
+          <t>1402-547-SE26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>32.98</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1402-547-SE26</t>
+          <t>1402-548-SE26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>54.4</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>889473-1707-CM26</t>
+          <t>889473-1715-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16999,12 +16999,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>145.13</v>
+        <v>168.6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>889473-1713-CM26</t>
+          <t>889473-1707-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17064,12 +17064,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>321.7</v>
+        <v>145.13</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>889473-1715-CM26</t>
+          <t>889473-1713-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>168.6</v>
+        <v>321.7</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>889473-1744-CM26</t>
+          <t>889473-1746-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>203.87</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>889473-1746-CM26</t>
+          <t>889473-1744-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>214.1</v>
+        <v>203.87</v>
       </c>
     </row>
     <row r="260">
@@ -17349,7 +17349,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1208100-30-CM26</t>
+          <t>889473-1763-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>642.91</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>889473-1763-CM26</t>
+          <t>1208100-31-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17439,12 +17439,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>184.48</v>
+        <v>152.79</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1208100-31-CM26</t>
+          <t>1208100-30-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17538,7 +17538,527 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>152.79</v>
+        <v>642.91</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>889473-1823-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>239.18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>889473-1825-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>149.32</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>889473-1834-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>233.58</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>889473-1869-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>357.1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1208100-33-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>LATAM AIRLINES GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>89.862.200-2</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>356.12</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2401-981-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>69.080.100-0</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>JetSMART</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>76.574.879-8</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>614.8099999999999</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1211-95-CM26</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>60.901.008-8</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>2181.78</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>889473-1968-CM26</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2239-16-LR23</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>61.980.530-5</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>SKY AIRLINE S A</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>88.417.000-1</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>225.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
+++ b/docs/oc-regiones/pasajes-aereos-nacionales/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M271"/>
+  <dimension ref="A1:M270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14034,12 +14034,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4562-290-CM26</t>
+          <t>4562-291-SE26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>380.76</v>
+        <v>116.58</v>
       </c>
     </row>
     <row r="211">
@@ -14294,12 +14294,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4562-291-SE26</t>
+          <t>4562-290-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>116.58</v>
+        <v>380.76</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2401-568-CM26</t>
+          <t>2401-569-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>490.38</v>
+        <v>249.88</v>
       </c>
     </row>
     <row r="216">
@@ -14489,7 +14489,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2401-569-CM26</t>
+          <t>2401-568-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14548,7 +14548,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>249.88</v>
+        <v>490.38</v>
       </c>
     </row>
     <row r="218">
@@ -16049,7 +16049,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1402-503-CM26</t>
+          <t>1402-504-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>229.32</v>
+        <v>286.54</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>889473-1511-CM26</t>
+          <t>889473-1515-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>261.2</v>
+        <v>286.38</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>889473-1515-CM26</t>
+          <t>1402-503-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>286.38</v>
+        <v>229.32</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1402-504-CM26</t>
+          <t>889473-1582-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16284,12 +16284,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>286.54</v>
+        <v>425.52</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>889473-1582-CM26</t>
+          <t>1402-531-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>425.52</v>
+        <v>212.61</v>
       </c>
     </row>
     <row r="246">
@@ -16439,7 +16439,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1402-531-CM26</t>
+          <t>889473-1656-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>212.61</v>
+        <v>161</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>889473-1656-CM26</t>
+          <t>932-166-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>161</v>
+        <v>1752.08</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>932-166-CM26</t>
+          <t>932-165-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1752.08</v>
+        <v>2095.47</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>932-165-CM26</t>
+          <t>889473-1667-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,12 +16659,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2095.47</v>
+        <v>122.51</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>889473-1667-CM26</t>
+          <t>889473-1675-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -16758,18 +16758,18 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>122.51</v>
+        <v>210.45</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>889473-1675-CM26</t>
+          <t>1402-548-SE26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-23-LP10</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -16779,22 +16779,22 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16804,12 +16804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>210.45</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="253">
@@ -16894,12 +16894,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1402-548-SE26</t>
+          <t>889473-1715-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2239-23-LP10</t>
+          <t>2239-16-LR23</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -16909,22 +16909,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16934,12 +16934,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>LATAM AIRLINES GROUP S.A.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>89.862.200-2</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>32.98</v>
+        <v>168.6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>889473-1715-CM26</t>
+          <t>889473-1713-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>168.6</v>
+        <v>321.7</v>
       </c>
     </row>
     <row r="256">
@@ -17089,7 +17089,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>889473-1713-CM26</t>
+          <t>889473-1746-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>321.7</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>889473-1746-CM26</t>
+          <t>889473-1744-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>214.1</v>
+        <v>203.87</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>889473-1744-CM26</t>
+          <t>889473-1766-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>203.87</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>889473-1766-CM26</t>
+          <t>889473-1763-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>139.71</v>
+        <v>184.48</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>889473-1763-CM26</t>
+          <t>1208100-31-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>184.48</v>
+        <v>152.79</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1208100-31-CM26</t>
+          <t>1208100-30-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>152.79</v>
+        <v>642.91</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1208100-30-CM26</t>
+          <t>889473-1823-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17489,12 +17489,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>642.91</v>
+        <v>239.18</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>889473-1823-CM26</t>
+          <t>889473-1825-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>239.18</v>
+        <v>149.32</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>889473-1825-CM26</t>
+          <t>889473-1834-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>149.32</v>
+        <v>233.58</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>889473-1834-CM26</t>
+          <t>889473-1869-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>233.58</v>
+        <v>357.1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>889473-1869-CM26</t>
+          <t>1208100-33-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>357.1</v>
+        <v>356.12</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1208100-33-CM26</t>
+          <t>2401-981-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17819,22 +17819,22 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17844,12 +17844,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>LATAM AIRLINES GROUP S.A.</t>
+          <t>JetSMART</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>89.862.200-2</t>
+          <t>76.574.879-8</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>356.12</v>
+        <v>614.8099999999999</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2401-981-CM26</t>
+          <t>1211-95-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>60.901.008-8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17909,12 +17909,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>JetSMART</t>
+          <t>SKY AIRLINE S A</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.574.879-8</t>
+          <t>88.417.000-1</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>614.8099999999999</v>
+        <v>2181.78</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1211-95-CM26</t>
+          <t>889473-1968-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17949,22 +17949,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>60.901.008-8</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,71 +17993,6 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2181.78</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>889473-1968-CM26</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2239-16-LR23</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>61.980.530-5</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>SKY AIRLINE S A</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>88.417.000-1</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M271" s="2" t="n">
         <v>225.92</v>
       </c>
     </row>
